--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6277-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6277-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6139BA03-3CB3-47B4-8EC8-9EE98D8DE212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBCE9723-624A-4865-880E-44431C702130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{0AB569B4-D8DC-4774-96C7-D5409F4F5896}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{A4B076D9-E669-40D3-BC3F-49DE7DEF165F}"/>
   </bookViews>
   <sheets>
     <sheet name="6277-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1579,29 +1579,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DDC1DB-45D9-4263-B5BF-052265B8BCF6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323AB68E-5283-4424-A568-C6940471ED10}">
   <dimension ref="A1:X68"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="23" width="6.75" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="23" width="5.88671875" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1635,7 +1635,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1671,7 +1671,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1791,7 +1791,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="42"/>
@@ -1899,7 +1899,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>30</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>30</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>30</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>2024</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>30</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>30</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>30</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>30</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>30</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
         <v>2023</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>30</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>30</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>30</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>30</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>30</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="47">
         <v>2022</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
         <v>30</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>30</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
         <v>30</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
         <v>30</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
         <v>30</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="49">
         <v>2021</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>30</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>30</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>30</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>30</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>30</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="47">
         <v>2020</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>7.27</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
         <v>30</v>
       </c>
@@ -4109,7 +4109,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="18" t="s">
         <v>30</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
         <v>30</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="18" t="s">
         <v>30</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="18" t="s">
         <v>30</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="49">
         <v>2019</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
         <v>30</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
         <v>30</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
         <v>30</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
         <v>30</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="47">
         <v>2018</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="49">
         <v>2017</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="47">
         <v>2016</v>
       </c>
@@ -4989,7 +4989,7 @@
         <v>7.76</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="49">
         <v>2015</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>7.83</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="47">
         <v>2014</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>9.93</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="49">
         <v>2013</v>
       </c>
@@ -5205,7 +5205,7 @@
         <v>7.09</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="47">
         <v>2012</v>
       </c>
@@ -5277,7 +5277,7 @@
         <v>7.71</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="49">
         <v>2011</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>8.43</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="47">
         <v>2010</v>
       </c>
@@ -5421,7 +5421,7 @@
         <v>8.9499999999999993</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="49">
         <v>2009</v>
       </c>
@@ -5493,7 +5493,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="47">
         <v>2008</v>
       </c>
@@ -5565,7 +5565,7 @@
         <v>8.42</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="49">
         <v>2007</v>
       </c>
@@ -5637,7 +5637,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="47">
         <v>2006</v>
       </c>
@@ -5709,7 +5709,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="49">
         <v>2005</v>
       </c>
@@ -5781,7 +5781,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="47">
         <v>2004</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="49">
         <v>2003</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="62" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="47">
         <v>2002</v>
       </c>
@@ -5997,7 +5997,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="63" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="49">
         <v>2001</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="47">
         <v>2000</v>
       </c>
@@ -6141,7 +6141,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="49">
         <v>1999</v>
       </c>
@@ -6213,7 +6213,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="47">
         <v>1998</v>
       </c>
@@ -6285,7 +6285,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="49">
         <v>1997</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="47" t="s">
         <v>66</v>
       </c>
